--- a/Claude outputs/USULAN_TAMBAHAN_ANOMALI.xlsx
+++ b/Claude outputs/USULAN_TAMBAHAN_ANOMALI.xlsx
@@ -496,9 +496,24 @@
           <t>Apakah 407 sudah sesuai dengan Tnaggal+Bulan Pendataan - 406A+406B+406C dengan pembulatan ke bawah</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>M407, M406A, M406B, M406C</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>umur_hitung(M406A,M406B,M406C, acuan=7 Sep 2026) &lt;&gt; M407</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Apakah umur (M407) sudah sesuai dengan tanggal lahir, dihitung terhadap tanggal pendataan 7 September 2026 (pembulatan ke bawah)?</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>PERLU KLARIFIKASI: field "Tanggal Pendataan" belum ada di data yang tersimpan (m1 cuma punya M406A/B/C = komponen TANGGAL LAHIR, bukan tanggal survei/pendataan). Field tanggal pendataannya yang mana / dari file apa?</t>
+          <t>SUDAH DIIMPLEMENTASIKAN (16/9) sbg kode M-USIA-VS-TGL-LAHIR, sesuai klarifikasi Anda (acuan tetap 7 Sept 2026). Catatan: asumsi urutan M406A=tanggal, M406B=bulan, M406C=tahun belum dikonfirmasi eksplisit.</t>
         </is>
       </c>
     </row>
@@ -508,9 +523,24 @@
           <t>71. Umur 18 tahun ke atas tapi masih kelas 1 SMA</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>M407, M503, M504</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>M407 &gt; 18 AND M503 = 2 AND M504 &lt; 18</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Apakah benar umur 18 tahun ke atas tapi masih bersekolah di jenjang kode di bawah 18?</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>PERLU KLARIFIKASI: field "kelas" (tingkat/kelas DALAM jenjang, mis. kelas 1/2/3) belum teridentifikasi di data tersimpan. M504/M506 yang ada di data cuma kode JENJANG (SD/SMP/SMA/dst, dipakai M-03/M-04), bukan kelasnya. Field kelas ada di mana (nama field-nya)?</t>
+          <t>SUDAH DIIMPLEMENTASIKAN (16/9) sbg kode M-71, sesuai klarifikasi Anda.</t>
         </is>
       </c>
     </row>
@@ -520,9 +550,24 @@
           <t>68. Umur 13-15 tahun tapi sudah kelas 2-3 SMA</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>M407, M503, M504</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M407 13-15 AND M503 = 2 AND M504 13-16</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Apakah benar umur 13-15 tahun tapi masih bersekolah di jenjang kode 13-16?</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>PERLU KLARIFIKASI: field "kelas" (tingkat/kelas DALAM jenjang, mis. kelas 1/2/3) belum teridentifikasi di data tersimpan. M504/M506 yang ada di data cuma kode JENJANG (SD/SMP/SMA/dst, dipakai M-03/M-04), bukan kelasnya. Field kelas ada di mana (nama field-nya)?</t>
+          <t>SUDAH DIIMPLEMENTASIKAN (16/9) sbg kode M-68, sesuai klarifikasi Anda.</t>
         </is>
       </c>
     </row>
@@ -532,9 +577,24 @@
           <t>66. Umur 5 tahun tapi sudah kelas 1-3 SD</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>M407, M503, M504</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M407 &lt; 6 AND M503 = 2 AND M504 = 3</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Apakah benar umur kurang dari 6 tahun tapi sudah bersekolah di jenjang SD?</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>PERLU KLARIFIKASI: field "kelas" (tingkat/kelas DALAM jenjang, mis. kelas 1/2/3) belum teridentifikasi di data tersimpan. M504/M506 yang ada di data cuma kode JENJANG (SD/SMP/SMA/dst, dipakai M-03/M-04), bukan kelasnya. Field kelas ada di mana (nama field-nya)?</t>
+          <t>SUDAH DIIMPLEMENTASIKAN (16/9) sbg kode M-66, sesuai klarifikasi Anda.</t>
         </is>
       </c>
     </row>
@@ -544,9 +604,24 @@
           <t>65. Umur 8 tahun ke atas tetapi masih mengikuti TK pada tahun ajaran sebelumnya</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>M407, M508</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>M407 &gt; 7 AND M508 &gt; 0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Apakah benar umur lebih dari 7 tahun tapi M508 masih terisi?</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>⚠ TUMPANG TINDIH dengan M-17 yang SUDAH ADA di kode (cond: M403=3 AND M509=1 AND umur 8-10 th, field M403/M509/M407 terverifikasi ada di data). Usulan ini rentang usianya lebih luas ("8 tahun ke atas", tanpa batas atas) — mau M-17 diperluas rentangnya, atau ini memang dimaksudkan jadi kode terpisah M-65?</t>
+          <t>SUDAH DIIMPLEMENTASIKAN (16/9) sbg kode M-65. Field dikoreksi jadi M508 (bukan M509) — sudah TIDAK tumpang tindih dgn M-17.</t>
         </is>
       </c>
     </row>
@@ -573,7 +648,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SUDAH ADA di kode sbg M-61 — TAPI field-nya M1602H, bukan M1602G seperti di usulan ini. Sudah dikoreksi sebelumnya setelah baca kuesioner asli (huruf G = "Seminar/Sosialisasi/Penyuluhan", H = "Lainnya"). Tidak perlu diubah lagi, sudah benar di aplikasi.</t>
+          <t>Dikonfirmasi BENAR oleh Anda (16/9): field M1602H (bukan G). Sudah sesuai dgn kode M-61 yang sudah ada, tidak ada perubahan.</t>
         </is>
       </c>
     </row>
@@ -735,7 +810,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BELUM ADA di kode. Field M1405 terverifikasi ada di data (tabel mrt1/Blok 14), kondisi jelas dari deskripsi Anda (kode 4 = lainnya, pola sama persis dgn M-56/57/58 yg sudah ada). Siap diimplementasikan kalau disetujui.</t>
+          <t>SUDAH DIIMPLEMENTASIKAN (16/9) sbg kode M-55.</t>
         </is>
       </c>
     </row>
@@ -752,7 +827,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>TIDAK BISA dipakai apa adanya: kondisi "M4101F=3 AND M1401F=4" kontradiktif diri sendiri (1 field tidak mungkin =3 DAN =4 sekaligus), dan "M4101F" kelihatannya typo dari "M1401F". Field M1401F sendiri terverifikasi ada di data (nilainya cuma 3/4). Yang dimaksud field kedua itu field apa (mis. M1401E)? Saya tidak berani menebak.</t>
+          <t>MASIH PERLU KLARIFIKASI — foto kuesioner yang Anda kirim itu utk Rincian 1402, sedangkan baris ini soal Rincian 1401 (field M1401F, beda rincian). Field M1401 di data cuma 6 kolom (M1401A-F, tanpa akhiran _1/_2) dgn pola nilai A/C/E berisi 1-2 dan B/D/F berisi 3-4 — kemungkinan pola serupa 1402 (3 topik x Menyelenggarakan/Menghadiri) tapi topik &amp; pertanyaan persis Rincian 1401 belum saya ketahui. Boleh minta foto/teks kuesioner utk Rincian 1401 juga?</t>
         </is>
       </c>
     </row>
@@ -762,14 +837,24 @@
           <t>53. Konfirmasi menyelenggarakan atau menghadiri upacara tradisi lainnyan</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>M1402G_1, M1402G_2</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>M1402G = 1 AND M1402G = 3</t>
+          <t>M1402G_1 = 1 OR M1402G_2 = 3</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Konfirmasi menyelenggarakan atau menghadiri upacara tradisi lainnya (Rincian 1402.G)? Upacara/tradisi apa?</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>TIDAK BISA dipakai apa adanya: kondisi "M1402G = 1 AND M1402G = 3" kontradiktif diri sendiri. Selain itu, field "M1402G" TIDAK ADA persis begitu di data — yang ada M1402G_1 dan M1402G_2 (field-nya kepisah 2 kolom). Yang dimaksud M1402G_1 dan M1402G_2 masing-masing bernilai berapa?</t>
+          <t>SUDAH DIIMPLEMENTASIKAN (16/9) sbg kode M-53. Field dikoreksi jadi M1402G_1 (Menyelenggarakan) &amp; M1402G_2 (Menghadiri) sesuai foto kuesioner — bukan M1402G tunggal, dan logikanya OR (bukan AND) karena "atau".</t>
         </is>
       </c>
     </row>
@@ -779,14 +864,24 @@
           <t>52. Konfirmasi menyelenggarakan dan atau menghadiri upacara tradisi panen</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>M1402F_1, M1402F_2</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>M1402F = 1 AND M1402F = 3</t>
+          <t>M1402F_1 = 1 OR M1402F_2 = 3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Konfirmasi menyelenggarakan dan/atau menghadiri upacara tradisi panen (Rincian 1402.F)?</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>TIDAK BISA dipakai apa adanya: kondisi "M1402F = 1 AND M1402F = 3" kontradiktif diri sendiri. Field "M1402F" juga TIDAK ADA persis begitu di data — yang ada M1402F_1 dan M1402F_2. Yang dimaksud M1402F_1 dan M1402F_2 masing-masing bernilai berapa?</t>
+          <t>SUDAH DIIMPLEMENTASIKAN (16/9) sbg kode M-52. Field dikoreksi jadi M1402F_1 (Menyelenggarakan) &amp; M1402F_2 (Menghadiri) sesuai foto kuesioner — bukan M1402F tunggal, dan logikanya OR (bukan AND) karena "dan/atau".</t>
         </is>
       </c>
     </row>
@@ -813,7 +908,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BELUM ADA di kode. Field M1216 terverifikasi ada di data, kondisi sudah jelas dari usulan Anda (kolom E). Siap diimplementasikan kalau disetujui.</t>
+          <t>SUDAH DIIMPLEMENTASIKAN (16/9) sbg kode M-51.</t>
         </is>
       </c>
     </row>
@@ -840,7 +935,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>BELUM ADA di kode. Field M1215 terverifikasi ada di data, kondisi sudah jelas dari usulan Anda (kolom E). Siap diimplementasikan kalau disetujui.</t>
+          <t>SUDAH DIIMPLEMENTASIKAN (16/9) sbg kode M-50.</t>
         </is>
       </c>
     </row>
@@ -867,7 +962,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>BELUM ADA di kode. Field M1208 terverifikasi ada di data. Kolom E &amp; F di usulan ini sudah lengkap — siap diimplementasikan kalau disetujui.</t>
+          <t>SUDAH DIIMPLEMENTASIKAN (16/9) sbg kode M-49.</t>
         </is>
       </c>
     </row>

--- a/Claude outputs/USULAN_TAMBAHAN_ANOMALI.xlsx
+++ b/Claude outputs/USULAN_TAMBAHAN_ANOMALI.xlsx
@@ -820,14 +820,24 @@
           <t>Konfirmasi apakah memang membeli atau menggunakan perlengkapan upacara adat?</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>M1401F</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>M4101F =3 AND M1401F = 4</t>
+          <t>M1401F = 3</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Konfirmasi apakah benar ada ART yang membeli atau menggunakan perlengkapan upacara adat/tradisi (keris, guci, tombak, bokor, tempayan, dll.) dalam 3 bulan terakhir (Rincian 1401.F)?</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MASIH PERLU KLARIFIKASI — foto kuesioner yang Anda kirim itu utk Rincian 1402, sedangkan baris ini soal Rincian 1401 (field M1401F, beda rincian). Field M1401 di data cuma 6 kolom (M1401A-F, tanpa akhiran _1/_2) dgn pola nilai A/C/E berisi 1-2 dan B/D/F berisi 3-4 — kemungkinan pola serupa 1402 (3 topik x Menyelenggarakan/Menghadiri) tapi topik &amp; pertanyaan persis Rincian 1401 belum saya ketahui. Boleh minta foto/teks kuesioner utk Rincian 1401 juga?</t>
+          <t>SUDAH DIIMPLEMENTASIKAN (16/9) sbg kode M-PERLENGKAPAN-ADAT. Kondisi disederhanakan jadi M1401F=3 saja (kondisi ganda di draf awal typo &amp; kontradiktif). Kodebook (Ya=3/Tidak=4) dikonfirmasi dari foto kuesioner Rincian 1401.</t>
         </is>
       </c>
     </row>
